--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486894_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486894_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6347</v>
+        <v>9.051399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9479</v>
+        <v>8.1571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6868</v>
+        <v>0.8943</v>
       </c>
       <c r="G2" t="n">
         <v>5.4916</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6516</v>
+        <v>-1.2349</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4147</v>
+        <v>-0.2055</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2369</v>
+        <v>-1.0294</v>
       </c>
       <c r="V2" t="n">
         <v>2.9466</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.23</v>
+        <v>3.5874</v>
       </c>
       <c r="E3" t="n">
-        <v>3.847</v>
+        <v>4.0562</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6171</v>
+        <v>-0.4689</v>
       </c>
       <c r="G3" t="n">
         <v>2.9339</v>
@@ -688,13 +688,13 @@
         <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0674</v>
+        <v>-0.71</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3489</v>
+        <v>-0.1397</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7185</v>
+        <v>-0.5703</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2793</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8659</v>
+        <v>2.1484</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3651</v>
+        <v>2.4697</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4992</v>
+        <v>-0.3213</v>
       </c>
       <c r="G4" t="n">
         <v>1.3676</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7687</v>
+        <v>-0.4862</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.283</v>
+        <v>-0.1784</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4857</v>
+        <v>-0.3078</v>
       </c>
       <c r="V4" t="n">
         <v>0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7146</v>
+        <v>2.0581</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0754</v>
+        <v>2.3893</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3608</v>
+        <v>-0.3312</v>
       </c>
       <c r="G5" t="n">
         <v>0.6775</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2277</v>
+        <v>-0.8843</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.527</v>
+        <v>-0.2132</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7008</v>
+        <v>-0.6711</v>
       </c>
       <c r="V5" t="n">
         <v>3.4969</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4476</v>
+        <v>0.5243</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7322</v>
+        <v>2.046</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2846</v>
+        <v>-1.5217</v>
       </c>
       <c r="G6" t="n">
         <v>1.1793</v>
@@ -922,13 +922,13 @@
         <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4442</v>
+        <v>-1.3676</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9222</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.522</v>
+        <v>-0.7592</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5195</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.036</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0962</v>
+        <v>1.2008</v>
       </c>
       <c r="F7" t="n">
         <v>-1.1322</v>
@@ -1000,10 +1000,10 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1395</v>
+        <v>0.2441</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1122</v>
+        <v>0.2168</v>
       </c>
       <c r="U7" t="n">
         <v>0.0272</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0568</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>1.2759</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3327</v>
+        <v>-1.3624</v>
       </c>
       <c r="G8" t="n">
         <v>0.6688</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2328</v>
+        <v>-0.2625</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0307</v>
+        <v>0.001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1088</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6102</v>
+        <v>-1.2814</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4191</v>
+        <v>0.8961</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0294</v>
+        <v>-2.1776</v>
       </c>
       <c r="G9" t="n">
         <v>-0.731</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.862</v>
+        <v>0.1908</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8096</v>
+        <v>0.2866</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0524</v>
+        <v>-0.0958</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7679</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8378</v>
+        <v>-1.6903</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5487</v>
+        <v>-0.3927</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3865</v>
+        <v>-1.2975</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3371</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4931</v>
+        <v>-0.3593</v>
       </c>
       <c r="T10" t="n">
-        <v>1.104</v>
+        <v>0.1626</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6108</v>
+        <v>-0.5219</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4579</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8646</v>
+        <v>-1.8925</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1094</v>
+        <v>-0.9002</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7551</v>
+        <v>-0.9923</v>
       </c>
       <c r="G11" t="n">
         <v>0.4325</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.681</v>
+        <v>-0.7089</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.527</v>
+        <v>-0.3178</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.154</v>
+        <v>-0.3912</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.4874</v>
+        <v>12.4875</v>
       </c>
       <c r="E12" t="n">
-        <v>21.1981</v>
+        <v>21.1982</v>
       </c>
       <c r="F12" t="n">
         <v>-8.710800000000001</v>
@@ -1396,7 +1396,7 @@
         <v>-1.2605</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.3184</v>
+        <v>-4.3185</v>
       </c>
       <c r="V12" t="n">
         <v>0.1315000000000009</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>I. CORRALIZA COBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.607</v>
+        <v>2.5805</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8542</v>
+        <v>2.8367</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2473</v>
+        <v>-0.2562</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7327</v>
+        <v>0.1277</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.7168</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8104</v>
+        <v>0.8445</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5058</v>
+        <v>1.0926</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2954</v>
+        <v>-0.7489</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2104</v>
+        <v>1.8415</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2385</v>
+        <v>-0.9649</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2177</v>
+        <v>0.0321</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0208</v>
+        <v>-0.997</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>2.428</v>
+        <v>0.8717</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1966</v>
+        <v>0.5655</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2314</v>
+        <v>0.3062</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5277</v>
+        <v>0.3491</v>
       </c>
       <c r="W13" t="n">
         <v>1.1786</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3491</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. CORRALIZA COBA</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3085</v>
+        <v>2.2263</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9413</v>
+        <v>3.3252</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6328</v>
+        <v>-1.0989</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1277</v>
+        <v>0.1261</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7168</v>
+        <v>1.5864</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8445</v>
+        <v>-1.4602</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0926</v>
+        <v>2.1463</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7489</v>
+        <v>2.7252</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8415</v>
+        <v>-0.579</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9649</v>
+        <v>-2.0201</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0321</v>
+        <v>-1.1389</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.997</v>
+        <v>-0.8813</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q14" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.7679</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.7679</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.5997</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.6701</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.0704</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3491</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1786</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.8295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.569</v>
+        <v>1.4023</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6976</v>
+        <v>1.599</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1286</v>
+        <v>-0.1967</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1261</v>
+        <v>-0.7327</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5864</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4602</v>
+        <v>-0.8104</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1463</v>
+        <v>0.5058</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7252</v>
+        <v>0.2954</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.579</v>
+        <v>0.2104</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0201</v>
+        <v>-1.2385</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1389</v>
+        <v>-0.2177</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8813</v>
+        <v>-1.0208</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1197</v>
+        <v>1.2233</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1899</v>
+        <v>0.9413</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0702</v>
+        <v>0.282</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7679</v>
+        <v>1.5277</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7679</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5052</v>
+        <v>0.9857</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8921</v>
+        <v>5.6213</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3869</v>
+        <v>-4.6356</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3658</v>
+        <v>4.1031</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3735</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0077</v>
+        <v>4.0094</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1859</v>
+        <v>7.4223</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8702</v>
+        <v>0.9767</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3157</v>
+        <v>6.4456</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-3.3192</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4967</v>
+        <v>-0.883</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3234</v>
+        <v>-2.4362</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6117</v>
+        <v>0.2111</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3408</v>
+        <v>0.1005</v>
       </c>
       <c r="U17" t="n">
-        <v>0.271</v>
+        <v>0.1106</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3491</v>
+        <v>-1.0698</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0698</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.264</v>
+        <v>0.4059</v>
       </c>
       <c r="E18" t="n">
-        <v>5.0983</v>
+        <v>0.6829</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8344</v>
+        <v>-0.277</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1031</v>
+        <v>0.3658</v>
       </c>
       <c r="H18" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.3735</v>
       </c>
       <c r="I18" t="n">
-        <v>4.0094</v>
+        <v>-0.0077</v>
       </c>
       <c r="J18" t="n">
-        <v>7.4223</v>
+        <v>1.1859</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9767</v>
+        <v>0.8702</v>
       </c>
       <c r="L18" t="n">
-        <v>6.4456</v>
+        <v>0.3157</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3192</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.883</v>
+        <v>-0.4967</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4362</v>
+        <v>-0.3234</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2588</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5106000000000001</v>
+        <v>0.5123</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4225</v>
+        <v>0.1315</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0882</v>
+        <v>0.3808</v>
       </c>
       <c r="V18" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.0698</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1786</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.2484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7444</v>
+        <v>-1.446</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0964</v>
+        <v>-0.6601</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8408</v>
+        <v>-0.7859</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8442</v>
+        <v>-1.6407</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9863</v>
+        <v>-0.2145</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8579</v>
+        <v>-1.4261</v>
       </c>
       <c r="J19" t="n">
-        <v>0.589</v>
+        <v>0.5527</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6813</v>
+        <v>0.4477</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4332</v>
+        <v>-2.1934</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6676</v>
+        <v>-0.6623</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.5311</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4374</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.1861</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.6974</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.5075</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1899</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-1.4189</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.779</v>
+        <v>-1.5352</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7647</v>
+        <v>1.3056</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0143</v>
+        <v>-2.8408</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6407</v>
+        <v>-1.8442</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2145</v>
+        <v>-0.9863</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4261</v>
+        <v>-0.8579</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5527</v>
+        <v>0.589</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4477</v>
+        <v>0.6813</v>
       </c>
       <c r="L20" t="n">
-        <v>0.105</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1934</v>
+        <v>-2.4332</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6623</v>
+        <v>-1.6676</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5311</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.549</v>
+        <v>0.9066</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2907</v>
+        <v>0.7167</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2583</v>
+        <v>0.1899</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1332</v>
+        <v>-5.1594</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0852</v>
+        <v>-3.4386</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0481</v>
+        <v>-1.7209</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6791</v>
+        <v>-1.1283</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0794</v>
+        <v>0.4668</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5997</v>
+        <v>-1.5951</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1439</v>
+        <v>0.1915</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7489</v>
+        <v>1.3237</v>
       </c>
       <c r="L21" t="n">
-        <v>0.605</v>
+        <v>-1.1322</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5352</v>
+        <v>-1.3198</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3305</v>
+        <v>-0.8569</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2047</v>
+        <v>-0.4629</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2855</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q21" t="n">
         <v>-4.1068</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3591</v>
+        <v>-0.4233</v>
       </c>
       <c r="T21" t="n">
-        <v>2.336</v>
+        <v>-0.3527</v>
       </c>
       <c r="U21" t="n">
-        <v>1.023</v>
+        <v>-0.0706</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5277</v>
+        <v>-0.9384</v>
       </c>
       <c r="W21" t="n">
         <v>0.8295</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9353</v>
+        <v>-5.5477</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0662</v>
+        <v>-0.8268</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8691</v>
+        <v>-4.7209</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1283</v>
+        <v>-6.3796</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4668</v>
+        <v>-2.3457</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5951</v>
+        <v>-4.0339</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1915</v>
+        <v>-2.7655</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3237</v>
+        <v>-0.5416</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1322</v>
+        <v>-2.2239</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3198</v>
+        <v>-3.6142</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8569</v>
+        <v>-1.8041</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4629</v>
+        <v>-1.8101</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.6694</v>
+        <v>0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1991</v>
+        <v>0.6266</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9804</v>
+        <v>0.6081</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2188</v>
+        <v>0.0185</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8295</v>
+        <v>2.3573</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7679</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3235</v>
+        <v>-6.8767</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4544</v>
+        <v>-2.2358</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.8691</v>
+        <v>-4.6409</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.3796</v>
+        <v>-3.6791</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3457</v>
+        <v>-2.0794</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.0339</v>
+        <v>-1.5997</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7655</v>
+        <v>-0.1439</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5416</v>
+        <v>-0.7489</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2239</v>
+        <v>0.605</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.6142</v>
+        <v>-3.5352</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8041</v>
+        <v>-1.3305</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8101</v>
+        <v>-2.2047</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2053</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1492</v>
+        <v>1.6156</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0195</v>
+        <v>1.1854</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1297</v>
+        <v>0.4302</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.5277</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3573</v>
+        <v>0.8295</v>
       </c>
       <c r="X23" t="n">
         <v>-2.3573</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.4874</v>
+        <v>-11.79</v>
       </c>
       <c r="E24" t="n">
-        <v>8.710700000000001</v>
+        <v>8.710699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.1984</v>
+        <v>-20.5008</v>
       </c>
       <c r="G24" t="n">
         <v>-9.7211</v>
@@ -2296,13 +2296,13 @@
         <v>-2.6286</v>
       </c>
       <c r="I24" t="n">
-        <v>-7.092299999999999</v>
+        <v>-7.0923</v>
       </c>
       <c r="J24" t="n">
         <v>12.3315</v>
       </c>
       <c r="K24" t="n">
-        <v>6.7831</v>
+        <v>6.783100000000001</v>
       </c>
       <c r="L24" t="n">
         <v>5.548299999999999</v>
@@ -2311,7 +2311,7 @@
         <v>-22.0526</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.411899999999999</v>
+        <v>-9.411900000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-12.6408</v>
@@ -2326,16 +2326,16 @@
         <v>11.2941</v>
       </c>
       <c r="S24" t="n">
-        <v>5.578999999999999</v>
+        <v>6.2761</v>
       </c>
       <c r="T24" t="n">
-        <v>4.3184</v>
+        <v>4.3183</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2604</v>
+        <v>1.9578</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1315000000000005</v>
+        <v>-0.1315000000000006</v>
       </c>
       <c r="W24" t="n">
         <v>11.5684</v>
